--- a/task138/golden/kbid_order_2027.xlsx
+++ b/task138/golden/kbid_order_2027.xlsx
@@ -9,9 +9,8 @@
   <sheets>
     <sheet name="Order 2027" sheetId="1" r:id="rId1"/>
     <sheet name="Replays" sheetId="2" r:id="rId2"/>
-    <sheet name="Root zone 31 Jan" sheetId="3" r:id="rId3"/>
-    <sheet name="Laterals 2026" sheetId="4" r:id="rId4"/>
-    <sheet name="Notes" sheetId="5" r:id="rId5"/>
+    <sheet name="Laterals 2026" sheetId="3" r:id="rId3"/>
+    <sheet name="Notes" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Replays'!$3:$3</definedName>
@@ -26,21 +25,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
-  <si>
-    <t>Kestrel Bend Irrigation District: 2027 water order, Tolan Valley Project</t>
-  </si>
-  <si>
-    <t>Water Order Procedure (rev. December 2025), Tables for the 2027 order. Prepared 1 February 2027.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+  <si>
+    <t>Kestrel Bend Irrigation District orders 215,000 acre-feet from the Tolan Valley Project for 2027</t>
+  </si>
+  <si>
+    <t>Water Resources, under the Water Order Procedure (rev. December 2025) and its tables for the 2027 order. Prepared 1 February 2027.</t>
   </si>
   <si>
     <t>2027 order (acre-feet)</t>
   </si>
   <si>
-    <t>Weather year whose replay sets the order</t>
-  </si>
-  <si>
-    <t>Headgate requirement in that replay (acre-feet)</t>
+    <t>Season</t>
+  </si>
+  <si>
+    <t>1 February to 31 October 2027</t>
   </si>
   <si>
     <t>Replayed seasons the order covers</t>
@@ -49,49 +48,16 @@
     <t>24 of 30 (weather years 1997 to 2026)</t>
   </si>
   <si>
-    <t>Monthly schedule (WOP 5.1)</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Acre-feet</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>March</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>July</t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
-    <t>September</t>
-  </si>
-  <si>
-    <t>October</t>
-  </si>
-  <si>
-    <t>Season</t>
-  </si>
-  <si>
-    <t>Each replay starts from the root-zone depletion each field carries at the end of 31 January 2027 (its last 2026 delivery, then the record's weather to 31 January).</t>
-  </si>
-  <si>
-    <t>Headgate requirement of the 2027 fields in each replayed weather year (WOP 2.4)</t>
+    <t>Replay that sets the order</t>
+  </si>
+  <si>
+    <t>Each replay starts every field from its root zone at the end of 31 January 2027, from its 2026 water and the record's weather since (Notes).</t>
+  </si>
+  <si>
+    <t>The order covers 24 of the 30 replayed weather years; six would need more</t>
+  </si>
+  <si>
+    <t>Headgate requirement of the 2027 fields with each weather year's 1 February to 31 October weather (WOP 2.4).</t>
   </si>
   <si>
     <t>Weather year</t>
@@ -112,118 +78,85 @@
     <t>no</t>
   </si>
   <si>
-    <t>Root zone at the end of 31 January 2027, 2027 fields by crop</t>
-  </si>
-  <si>
-    <t>Crop</t>
+    <t>Lateral 4 lost the largest share of its water in 2026: 14.9 per cent against a 13.8 per cent allowance</t>
+  </si>
+  <si>
+    <t>From the riders' meter book with the meter shop's work orders, the heading loggers' daily totals with the Water Master's estimates, and the riders' tail weir sheets.</t>
+  </si>
+  <si>
+    <t>Lateral</t>
+  </si>
+  <si>
+    <t>Turnout deliveries (acre-feet)</t>
+  </si>
+  <si>
+    <t>Water put in at the heading (acre-feet)</t>
+  </si>
+  <si>
+    <t>Share of the water put in not delivered (%)</t>
+  </si>
+  <si>
+    <t>Over the tail weir (acre-feet)</t>
+  </si>
+  <si>
+    <t>Loss allowance, Table 5 (%)</t>
+  </si>
+  <si>
+    <t>Lateral 1</t>
+  </si>
+  <si>
+    <t>Lateral 2</t>
+  </si>
+  <si>
+    <t>Lateral 3</t>
+  </si>
+  <si>
+    <t>Lateral 4</t>
+  </si>
+  <si>
+    <t>Lateral 5</t>
+  </si>
+  <si>
+    <t>Lateral 6</t>
+  </si>
+  <si>
+    <t>Lateral 7</t>
+  </si>
+  <si>
+    <t>Lateral 8</t>
+  </si>
+  <si>
+    <t>Lateral 9</t>
+  </si>
+  <si>
+    <t>Nine laterals</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Smallest whole number of thousands of acre-feet that would have covered the 2027 headgate requirement in at least 24 of the weather years 1997 to 2026 (WOP 2.3).</t>
   </si>
   <si>
     <t>Fields</t>
   </si>
   <si>
-    <t>Acres</t>
-  </si>
-  <si>
-    <t>Mean depletion (in, acre-weighted)</t>
-  </si>
-  <si>
-    <t>Fields at or past allowable depletion</t>
-  </si>
-  <si>
-    <t>Almonds</t>
-  </si>
-  <si>
-    <t>Pistachios</t>
-  </si>
-  <si>
-    <t>Walnuts</t>
-  </si>
-  <si>
-    <t>Wine grapes</t>
-  </si>
-  <si>
-    <t>Citrus (oranges)</t>
-  </si>
-  <si>
-    <t>Alfalfa</t>
-  </si>
-  <si>
-    <t>Irrigated pasture</t>
-  </si>
-  <si>
-    <t>All 2027 fields</t>
-  </si>
-  <si>
-    <t>2026 season on each lateral, from the meter book, the heading flumes and the tail weir sheets</t>
-  </si>
-  <si>
-    <t>Lateral</t>
-  </si>
-  <si>
-    <t>Water put in at the heading (acre-feet)</t>
-  </si>
-  <si>
-    <t>Turnout deliveries (acre-feet)</t>
-  </si>
-  <si>
-    <t>Share of the water put in not delivered (%)</t>
-  </si>
-  <si>
-    <t>Over the tail weir (acre-feet)</t>
-  </si>
-  <si>
-    <t>Loss allowance, Table 5 (%)</t>
-  </si>
-  <si>
-    <t>Lateral 1</t>
-  </si>
-  <si>
-    <t>Lateral 2</t>
-  </si>
-  <si>
-    <t>Lateral 3</t>
-  </si>
-  <si>
-    <t>Lateral 4</t>
-  </si>
-  <si>
-    <t>Lateral 5</t>
-  </si>
-  <si>
-    <t>Lateral 6</t>
-  </si>
-  <si>
-    <t>Lateral 7</t>
-  </si>
-  <si>
-    <t>Lateral 8</t>
-  </si>
-  <si>
-    <t>Lateral 9</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Order</t>
-  </si>
-  <si>
-    <t>The smallest whole number of hundreds of acre-feet that would have covered the 2027 headgate requirement in at least 24 of the thirty weather years 1997 to 2026 (WOP 2.3).</t>
-  </si>
-  <si>
-    <t>Each field on its latest accepted 2027 water request, with the crop, irrigation method and acres on the request and the turnout, lateral and soil unit in the field register as it stood on 1 February 2027 (WOP 6.2). Withdrawn requests and superseded versions are not run.</t>
-  </si>
-  <si>
-    <t>Start of each replay</t>
-  </si>
-  <si>
-    <t>The root-zone depletion each field carries at the end of 31 January 2027: zero at the end of the day of its last delivered 2026 set in the irrigation orders, then the daily balance of WOP 3.1 on the District's weather record to 31 January.</t>
+    <t>Latest accepted 2027 request for each field: crop, method and acres from the request; turnout, lateral and soil unit from the register as it stood on 1 February 2027 (WOP 6.2). Withdrawn requests and superseded versions not run.</t>
+  </si>
+  <si>
+    <t>Root zone at 31 January</t>
+  </si>
+  <si>
+    <t>Each field run day by day through the WOP 3.1 balance from the end of 27 January 2026, when the winter's rains had every root zone at field capacity, to the end of 31 January 2027: each delivered 2026 set in the irrigation orders at its ordered flow for the hours it ran, times the Table 4 efficiency of the field's method, on the record's weather. Cancelled orders carry no water.</t>
   </si>
   <si>
     <t>Weather record</t>
@@ -232,22 +165,16 @@
     <t>Station 39 to 30 April 2014 and the yard station from 1 May 2014; a day the yard station did not record takes station 39's values (WOP 6.1).</t>
   </si>
   <si>
-    <t>Monthly schedule</t>
-  </si>
-  <si>
-    <t>The order times each month's share of the thirty replays' summed monthly requirements, to the nearest 10 acre-feet; October takes the difference (WOP 5.1).</t>
-  </si>
-  <si>
     <t>Laterals 2026</t>
   </si>
   <si>
-    <t>Deliveries from the riders' meter reads, each meter changed during the season chained through the meter shop's removal and installation readings; the Lateral 5 tail turnouts (05-045 to 05-058) on Lateral 5 to their 15 June 2026 reads and on Lateral 6 after. Water put in from the heading flumes' daily volumes, the Water Master's estimated days included. Tail weir spill from the riders' morning gauge readings, each standing until the next reading, the crest raised 2 inches for each flashboard in place.</t>
+    <t>Deliveries from the riders' meter reads, a meter changed in the season chained through the shop's register readings at the change; the west spur turnouts (05-021 to 05-034) on Lateral 5 to their 15 June reads and on Lateral 6 after. Water put in from the heading loggers' daily totals, with the Water Master's estimates (operations log) for the days a logger kept no total. Tail weir spill from the riders' morning gauge readings, each standing until the next reading, the crest raised 2 inches for each board in place.</t>
   </si>
   <si>
     <t>Rounding</t>
   </si>
   <si>
-    <t>The order to the whole hundred acre-feet, other volumes to the nearest 10 acre-feet, shares to one decimal place; figures are carried unrounded until shown.</t>
+    <t>Order to the whole thousand acre-feet; other volumes to the nearest 10 acre-feet; shares to one decimal place. Figures carried unrounded until shown.</t>
   </si>
 </sst>
 </file>
@@ -257,7 +184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,14 +203,6 @@
     <font>
       <i/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -340,23 +259,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -665,11 +582,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6FB07B-A68E-5865-B591-09B0A7C66575}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -687,129 +604,36 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>202700</v>
+        <v>215000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>2012</v>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4">
-        <v>202660</v>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>2012</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4">
-        <v>13520</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4">
-        <v>10290</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4">
-        <v>27190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4">
-        <v>37470</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4">
-        <v>42010</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4">
-        <v>37270</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4">
-        <v>24010</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4">
-        <v>9970</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4">
-        <v>202700</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -829,22 +653,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>21</v>
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>25</v>
+      <c r="A3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -852,13 +681,13 @@
         <v>1997</v>
       </c>
       <c r="B4" s="4">
-        <v>192420</v>
+        <v>203280</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -866,13 +695,13 @@
         <v>1998</v>
       </c>
       <c r="B5" s="4">
-        <v>201070</v>
+        <v>212190</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -880,13 +709,13 @@
         <v>1999</v>
       </c>
       <c r="B6" s="4">
-        <v>199450</v>
+        <v>210940</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -894,13 +723,13 @@
         <v>2000</v>
       </c>
       <c r="B7" s="4">
-        <v>201410</v>
+        <v>212450</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -908,13 +737,13 @@
         <v>2001</v>
       </c>
       <c r="B8" s="4">
-        <v>195890</v>
+        <v>207140</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -922,13 +751,13 @@
         <v>2002</v>
       </c>
       <c r="B9" s="4">
-        <v>211090</v>
+        <v>221980</v>
       </c>
       <c r="C9">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,13 +765,13 @@
         <v>2003</v>
       </c>
       <c r="B10" s="4">
-        <v>204980</v>
+        <v>215850</v>
       </c>
       <c r="C10">
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -950,13 +779,13 @@
         <v>2004</v>
       </c>
       <c r="B11" s="4">
-        <v>191260</v>
+        <v>201970</v>
       </c>
       <c r="C11">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -964,13 +793,13 @@
         <v>2005</v>
       </c>
       <c r="B12" s="4">
-        <v>210490</v>
+        <v>220500</v>
       </c>
       <c r="C12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -978,13 +807,13 @@
         <v>2006</v>
       </c>
       <c r="B13" s="4">
-        <v>198490</v>
+        <v>209240</v>
       </c>
       <c r="C13">
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -992,13 +821,13 @@
         <v>2007</v>
       </c>
       <c r="B14" s="4">
-        <v>183350</v>
+        <v>195230</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1006,13 +835,13 @@
         <v>2008</v>
       </c>
       <c r="B15" s="4">
-        <v>201140</v>
+        <v>212090</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,13 +849,13 @@
         <v>2009</v>
       </c>
       <c r="B16" s="4">
-        <v>208110</v>
+        <v>218900</v>
       </c>
       <c r="C16">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1034,13 +863,13 @@
         <v>2010</v>
       </c>
       <c r="B17" s="4">
-        <v>206750</v>
+        <v>217900</v>
       </c>
       <c r="C17">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1048,13 +877,13 @@
         <v>2011</v>
       </c>
       <c r="B18" s="4">
-        <v>201290</v>
+        <v>212940</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,13 +891,13 @@
         <v>2012</v>
       </c>
       <c r="B19" s="4">
-        <v>202660</v>
+        <v>214500</v>
       </c>
       <c r="C19">
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1076,13 +905,13 @@
         <v>2013</v>
       </c>
       <c r="B20" s="4">
-        <v>192270</v>
+        <v>204240</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1090,13 +919,13 @@
         <v>2014</v>
       </c>
       <c r="B21" s="4">
-        <v>194600</v>
+        <v>205910</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1104,13 +933,13 @@
         <v>2015</v>
       </c>
       <c r="B22" s="4">
-        <v>190970</v>
+        <v>202300</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1118,13 +947,13 @@
         <v>2016</v>
       </c>
       <c r="B23" s="4">
-        <v>182350</v>
+        <v>192450</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1132,13 +961,13 @@
         <v>2017</v>
       </c>
       <c r="B24" s="4">
-        <v>189570</v>
+        <v>201490</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,13 +975,13 @@
         <v>2018</v>
       </c>
       <c r="B25" s="4">
-        <v>191860</v>
+        <v>202830</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1160,13 +989,13 @@
         <v>2019</v>
       </c>
       <c r="B26" s="4">
-        <v>193590</v>
+        <v>205100</v>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1174,13 +1003,13 @@
         <v>2020</v>
       </c>
       <c r="B27" s="4">
-        <v>196970</v>
+        <v>208500</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1188,13 +1017,13 @@
         <v>2021</v>
       </c>
       <c r="B28" s="4">
-        <v>210400</v>
+        <v>220950</v>
       </c>
       <c r="C28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1202,13 +1031,13 @@
         <v>2022</v>
       </c>
       <c r="B29" s="4">
-        <v>200730</v>
+        <v>210890</v>
       </c>
       <c r="C29">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,13 +1045,13 @@
         <v>2023</v>
       </c>
       <c r="B30" s="4">
-        <v>188100</v>
+        <v>199120</v>
       </c>
       <c r="C30">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1230,13 +1059,13 @@
         <v>2024</v>
       </c>
       <c r="B31" s="4">
-        <v>156210</v>
+        <v>167020</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1244,13 +1073,13 @@
         <v>2025</v>
       </c>
       <c r="B32" s="4">
-        <v>197300</v>
+        <v>207030</v>
       </c>
       <c r="C32">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1258,13 +1087,13 @@
         <v>2026</v>
       </c>
       <c r="B33" s="4">
-        <v>195600</v>
+        <v>201240</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1273,397 +1102,245 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F297B9-E7BE-5EDE-BB2A-CBF903005F26}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4">
-        <v>184</v>
-      </c>
-      <c r="C4" s="4">
-        <v>11514</v>
-      </c>
-      <c r="D4" s="9">
-        <v>4.66</v>
-      </c>
-      <c r="E4">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5">
-        <v>80</v>
-      </c>
-      <c r="C5" s="4">
-        <v>5148</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1.67</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3226</v>
-      </c>
-      <c r="D6" s="9">
-        <v>3.28</v>
-      </c>
-      <c r="E6">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7">
-        <v>84</v>
-      </c>
-      <c r="C7" s="4">
-        <v>5029</v>
-      </c>
-      <c r="D7" s="9">
-        <v>3.21</v>
-      </c>
-      <c r="E7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8">
-        <v>49</v>
-      </c>
-      <c r="C8" s="4">
-        <v>3342</v>
-      </c>
-      <c r="D8" s="9">
-        <v>1.71</v>
-      </c>
-      <c r="E8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9">
-        <v>101</v>
-      </c>
-      <c r="C9" s="4">
-        <v>6632</v>
-      </c>
-      <c r="D9" s="9">
-        <v>4.07</v>
-      </c>
-      <c r="E9">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10">
-        <v>71</v>
-      </c>
-      <c r="C10" s="4">
-        <v>4508</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2.63</v>
-      </c>
-      <c r="E10">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="10">
-        <v>619</v>
-      </c>
-      <c r="C11" s="11">
-        <v>39399</v>
-      </c>
-      <c r="D11" s="12">
-        <v>3.39</v>
-      </c>
-      <c r="E11" s="10">
-        <v>446</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B7D713B-D7BF-5CE7-9642-A9803AE19CF9}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>42</v>
+      <c r="A1" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>48</v>
+      <c r="A3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4">
-        <v>19520</v>
+        <v>17870</v>
       </c>
       <c r="C4" s="4">
-        <v>17820</v>
-      </c>
-      <c r="D4" s="13">
-        <v>8.699999999999999</v>
+        <v>19680</v>
+      </c>
+      <c r="D4" s="8">
+        <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4">
         <v>580</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="8">
         <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4">
-        <v>21690</v>
+        <v>17530</v>
       </c>
       <c r="C5" s="4">
-        <v>19610</v>
-      </c>
-      <c r="D5" s="13">
-        <v>9.6</v>
+        <v>19410</v>
+      </c>
+      <c r="D5" s="8">
+        <v>9.699999999999999</v>
       </c>
       <c r="E5" s="4">
         <v>630</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="8">
         <v>10.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4">
-        <v>13990</v>
+        <v>15400</v>
       </c>
       <c r="C6" s="4">
-        <v>12800</v>
-      </c>
-      <c r="D6" s="13">
-        <v>8.5</v>
+        <v>16880</v>
+      </c>
+      <c r="D6" s="8">
+        <v>8.800000000000001</v>
       </c>
       <c r="E6" s="4">
         <v>440</v>
       </c>
-      <c r="F6" s="13">
-        <v>6.4</v>
+      <c r="F6" s="8">
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B7" s="4">
-        <v>19930</v>
+        <v>17890</v>
       </c>
       <c r="C7" s="4">
-        <v>16960</v>
-      </c>
-      <c r="D7" s="13">
+        <v>21020</v>
+      </c>
+      <c r="D7" s="8">
         <v>14.9</v>
       </c>
       <c r="E7" s="4">
         <v>270</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="8">
         <v>13.8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4">
-        <v>17990</v>
+        <v>18160</v>
       </c>
       <c r="C8" s="4">
-        <v>16500</v>
-      </c>
-      <c r="D8" s="13">
-        <v>8.300000000000001</v>
+        <v>19760</v>
+      </c>
+      <c r="D8" s="8">
+        <v>8.1</v>
       </c>
       <c r="E8" s="4">
         <v>550</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="8">
         <v>9.1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4">
-        <v>20090</v>
+        <v>18210</v>
       </c>
       <c r="C9" s="4">
-        <v>17300</v>
-      </c>
-      <c r="D9" s="13">
-        <v>13.9</v>
+        <v>21060</v>
+      </c>
+      <c r="D9" s="8">
+        <v>13.5</v>
       </c>
       <c r="E9" s="4">
         <v>650</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="8">
         <v>11.8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4">
-        <v>15090</v>
+        <v>15310</v>
       </c>
       <c r="C10" s="4">
-        <v>13880</v>
-      </c>
-      <c r="D10" s="13">
-        <v>8</v>
+        <v>16710</v>
+      </c>
+      <c r="D10" s="8">
+        <v>8.4</v>
       </c>
       <c r="E10" s="4">
         <v>510</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="8">
         <v>8.300000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4">
-        <v>16460</v>
+        <v>11490</v>
       </c>
       <c r="C11" s="4">
-        <v>14430</v>
-      </c>
-      <c r="D11" s="13">
-        <v>12.3</v>
+        <v>13110</v>
+      </c>
+      <c r="D11" s="8">
+        <v>12.4</v>
       </c>
       <c r="E11" s="4">
         <v>420</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="8">
         <v>9.699999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4">
-        <v>20980</v>
+        <v>15080</v>
       </c>
       <c r="C12" s="4">
-        <v>18210</v>
-      </c>
-      <c r="D12" s="13">
+        <v>17370</v>
+      </c>
+      <c r="D12" s="8">
         <v>13.2</v>
       </c>
       <c r="E12" s="4">
         <v>360</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="8">
         <v>12.6</v>
       </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="10">
+        <v>146940</v>
+      </c>
+      <c r="C13" s="10">
+        <v>164990</v>
+      </c>
+      <c r="D13" s="11">
+        <v>10.9</v>
+      </c>
+      <c r="E13" s="10">
+        <v>4410</v>
+      </c>
+      <c r="F13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1671,9 +1348,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89FE7BD-0D89-5C9A-9F82-2E02A93CF7BC}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -1681,72 +1358,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>58</v>
+      <c r="A1" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>60</v>
+      <c r="A3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>62</v>
+      <c r="A4" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>63</v>
+      <c r="A5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>65</v>
+      <c r="A6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>67</v>
+      <c r="A7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>69</v>
+      <c r="A8" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>73</v>
+      <c r="A9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/task138/golden/kbid_order_2027.xlsx
+++ b/task138/golden/kbid_order_2027.xlsx
@@ -25,9 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
-  <si>
-    <t>Kestrel Bend Irrigation District orders 215,000 acre-feet from the Tolan Valley Project for 2027</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
+  <si>
+    <t>Kestrel Bend Irrigation District orders 212,000 acre-feet from the Tolan Valley Project for 2027</t>
   </si>
   <si>
     <t>Water Resources, under the Water Order Procedure (rev. December 2025) and its tables for the 2027 order. Prepared 1 February 2027.</t>
@@ -51,7 +51,7 @@
     <t>Replay that sets the order</t>
   </si>
   <si>
-    <t>Each replay starts every field from its root zone at the end of 31 January 2027, from its 2026 water and the record's weather since (Notes).</t>
+    <t>Each replay starts every field from its root zone at the end of 31 January 2027, from its 2026 water at the share the soil moisture stations show reached the root zone, and the record's weather since (Notes).</t>
   </si>
   <si>
     <t>The order covers 24 of the 30 replayed weather years; six would need more</t>
@@ -156,7 +156,13 @@
     <t>Root zone at 31 January</t>
   </si>
   <si>
-    <t>Each field run day by day through the WOP 3.1 balance from the end of 27 January 2026, when the winter's rains had every root zone at field capacity, to the end of 31 January 2027: each delivered 2026 set in the irrigation orders at its ordered flow for the hours it ran, times the Table 4 efficiency of the field's method, on the record's weather. Cancelled orders carry no water.</t>
+    <t>Each field run day by day through the WOP 3.1 to 3.3 balance from the end of 27 January 2026, when the winter's rains had every root zone at field capacity, to the end of 31 January 2027 on the record's weather, each delivered 2026 set at its ordered flow for the hours it ran, times the share of it that reached the root zone. That share is the one the soil moisture network's 2026 readings give for the field's method: each drip, micro-sprinkler and sprinkler station's season fitted (least squares) by the share its own sets reached its root zone at, averaged over the method's stations, above Table 4 at every station; border fields at Table 4, their sets running past field capacity. Cancelled orders carry no water.</t>
+  </si>
+  <si>
+    <t>Replays</t>
+  </si>
+  <si>
+    <t>Each replay from that root zone, with WOP 3.4 and 3.5 as filed: an irrigation at the allowable depletion returns the field to field capacity and delivers the depletion over the Table 4 efficiency.</t>
   </si>
   <si>
     <t>Weather record</t>
@@ -604,7 +610,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>215000</v>
+        <v>212000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -681,10 +687,10 @@
         <v>1997</v>
       </c>
       <c r="B4" s="4">
-        <v>203280</v>
+        <v>200630</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -695,10 +701,10 @@
         <v>1998</v>
       </c>
       <c r="B5" s="4">
-        <v>212190</v>
+        <v>209310</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -709,10 +715,10 @@
         <v>1999</v>
       </c>
       <c r="B6" s="4">
-        <v>210940</v>
+        <v>207980</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -723,7 +729,7 @@
         <v>2000</v>
       </c>
       <c r="B7" s="4">
-        <v>212450</v>
+        <v>209600</v>
       </c>
       <c r="C7">
         <v>22</v>
@@ -737,7 +743,7 @@
         <v>2001</v>
       </c>
       <c r="B8" s="4">
-        <v>207140</v>
+        <v>204400</v>
       </c>
       <c r="C8">
         <v>15</v>
@@ -751,7 +757,7 @@
         <v>2002</v>
       </c>
       <c r="B9" s="4">
-        <v>221980</v>
+        <v>219470</v>
       </c>
       <c r="C9">
         <v>30</v>
@@ -765,7 +771,7 @@
         <v>2003</v>
       </c>
       <c r="B10" s="4">
-        <v>215850</v>
+        <v>213440</v>
       </c>
       <c r="C10">
         <v>25</v>
@@ -779,10 +785,10 @@
         <v>2004</v>
       </c>
       <c r="B11" s="4">
-        <v>201970</v>
+        <v>199840</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -793,7 +799,7 @@
         <v>2005</v>
       </c>
       <c r="B12" s="4">
-        <v>220500</v>
+        <v>218570</v>
       </c>
       <c r="C12">
         <v>28</v>
@@ -807,7 +813,7 @@
         <v>2006</v>
       </c>
       <c r="B13" s="4">
-        <v>209240</v>
+        <v>206650</v>
       </c>
       <c r="C13">
         <v>17</v>
@@ -821,7 +827,7 @@
         <v>2007</v>
       </c>
       <c r="B14" s="4">
-        <v>195230</v>
+        <v>192230</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -835,10 +841,10 @@
         <v>2008</v>
       </c>
       <c r="B15" s="4">
-        <v>212090</v>
+        <v>209420</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -849,7 +855,7 @@
         <v>2009</v>
       </c>
       <c r="B16" s="4">
-        <v>218900</v>
+        <v>216650</v>
       </c>
       <c r="C16">
         <v>27</v>
@@ -863,7 +869,7 @@
         <v>2010</v>
       </c>
       <c r="B17" s="4">
-        <v>217900</v>
+        <v>215600</v>
       </c>
       <c r="C17">
         <v>26</v>
@@ -877,7 +883,7 @@
         <v>2011</v>
       </c>
       <c r="B18" s="4">
-        <v>212940</v>
+        <v>210010</v>
       </c>
       <c r="C18">
         <v>23</v>
@@ -891,7 +897,7 @@
         <v>2012</v>
       </c>
       <c r="B19" s="4">
-        <v>214500</v>
+        <v>211560</v>
       </c>
       <c r="C19">
         <v>24</v>
@@ -905,10 +911,10 @@
         <v>2013</v>
       </c>
       <c r="B20" s="4">
-        <v>204240</v>
+        <v>200630</v>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -919,7 +925,7 @@
         <v>2014</v>
       </c>
       <c r="B21" s="4">
-        <v>205910</v>
+        <v>203010</v>
       </c>
       <c r="C21">
         <v>13</v>
@@ -933,10 +939,10 @@
         <v>2015</v>
       </c>
       <c r="B22" s="4">
-        <v>202300</v>
+        <v>198710</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -947,7 +953,7 @@
         <v>2016</v>
       </c>
       <c r="B23" s="4">
-        <v>192450</v>
+        <v>190210</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -961,10 +967,10 @@
         <v>2017</v>
       </c>
       <c r="B24" s="4">
-        <v>201490</v>
+        <v>198160</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -975,7 +981,7 @@
         <v>2018</v>
       </c>
       <c r="B25" s="4">
-        <v>202830</v>
+        <v>200450</v>
       </c>
       <c r="C25">
         <v>9</v>
@@ -989,7 +995,7 @@
         <v>2019</v>
       </c>
       <c r="B26" s="4">
-        <v>205100</v>
+        <v>202230</v>
       </c>
       <c r="C26">
         <v>12</v>
@@ -1003,7 +1009,7 @@
         <v>2020</v>
       </c>
       <c r="B27" s="4">
-        <v>208500</v>
+        <v>205530</v>
       </c>
       <c r="C27">
         <v>16</v>
@@ -1017,7 +1023,7 @@
         <v>2021</v>
       </c>
       <c r="B28" s="4">
-        <v>220950</v>
+        <v>218850</v>
       </c>
       <c r="C28">
         <v>29</v>
@@ -1031,10 +1037,10 @@
         <v>2022</v>
       </c>
       <c r="B29" s="4">
-        <v>210890</v>
+        <v>208190</v>
       </c>
       <c r="C29">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
@@ -1045,7 +1051,7 @@
         <v>2023</v>
       </c>
       <c r="B30" s="4">
-        <v>199120</v>
+        <v>196220</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -1059,7 +1065,7 @@
         <v>2024</v>
       </c>
       <c r="B31" s="4">
-        <v>167020</v>
+        <v>163360</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1073,7 +1079,7 @@
         <v>2025</v>
       </c>
       <c r="B32" s="4">
-        <v>207030</v>
+        <v>204160</v>
       </c>
       <c r="C32">
         <v>14</v>
@@ -1087,10 +1093,10 @@
         <v>2026</v>
       </c>
       <c r="B33" s="4">
-        <v>201240</v>
+        <v>198370</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
@@ -1350,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89FE7BD-0D89-5C9A-9F82-2E02A93CF7BC}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -1418,6 +1424,14 @@
         <v>49</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
